--- a/sprint-backlog/sprint2/SE-Sprint-2-SB.xlsx
+++ b/sprint-backlog/sprint2/SE-Sprint-2-SB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujee\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annopsangsila/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9DABEE-C32E-4F98-8C7E-AC82CAFCBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F281AD-B2ED-5841-9361-EE363C77E89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0709F1E1-F1F4-47FC-A275-7F1E846FF281}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{0709F1E1-F1F4-47FC-A275-7F1E846FF281}"/>
   </bookViews>
   <sheets>
     <sheet name="SprintBacklog" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="58">
   <si>
     <t>Sprint Backlog</t>
   </si>
@@ -202,7 +202,13 @@
     <t>663380614-8</t>
   </si>
   <si>
-    <t>สมาชิก กบุ่มที่ 5</t>
+    <t>Team Velocity =</t>
+  </si>
+  <si>
+    <t>Effort Remaining =</t>
+  </si>
+  <si>
+    <t>สมาชิก กลุ่มที่ 5</t>
   </si>
 </sst>
 </file>
@@ -213,7 +219,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -575,22 +581,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -627,13 +618,62 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -643,68 +683,36 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -722,7 +730,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="th-TH"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1739,7 +1747,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีม Office 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2036,47 +2044,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67D96CC-A143-4128-B829-B54D05A600A2}">
   <dimension ref="A1:AB84"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="30.5" x14ac:dyDescent="1.05"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.1796875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="57.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="57.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.36328125" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="7.36328125" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="0.1796875" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="0.1796875" style="1" customWidth="1"/>
-    <col min="17" max="18" width="8.6328125" style="1"/>
-    <col min="19" max="19" width="15.6328125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="25.6328125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8.6328125" style="1"/>
-    <col min="22" max="22" width="11.453125" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.6328125" style="1"/>
+    <col min="9" max="9" width="7.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="0.1640625" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="0.1640625" style="1" customWidth="1"/>
+    <col min="17" max="18" width="8.6640625" style="1"/>
+    <col min="19" max="19" width="15.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="25.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" style="1"/>
+    <col min="22" max="22" width="11.5" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
+    <row r="1" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -2086,128 +2094,128 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" ht="36" x14ac:dyDescent="1.2">
+    <row r="2" spans="1:22" ht="31" x14ac:dyDescent="0.35">
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
     </row>
-    <row r="3" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B3" s="16" t="s">
-        <v>55</v>
+    <row r="3" spans="1:22" ht="34" x14ac:dyDescent="0.5">
+      <c r="B3" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
     </row>
-    <row r="4" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B4" s="54" t="s">
+    <row r="4" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B4" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="40" t="s">
         <v>42</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
     </row>
-    <row r="5" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B5" s="54" t="s">
+    <row r="5" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B5" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="40" t="s">
         <v>41</v>
       </c>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
     </row>
-    <row r="6" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B6" s="54" t="s">
+    <row r="6" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B6" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="40" t="s">
         <v>43</v>
       </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
     </row>
-    <row r="7" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B7" s="54" t="s">
+    <row r="7" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="40" t="s">
         <v>44</v>
       </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B8" s="54" t="s">
+    <row r="8" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B8" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="40" t="s">
         <v>40</v>
       </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
     </row>
-    <row r="9" spans="1:22" ht="36" x14ac:dyDescent="1.2">
-      <c r="B9" s="54" t="s">
+    <row r="9" spans="1:22" ht="31" x14ac:dyDescent="0.35">
+      <c r="B9" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="40" t="s">
         <v>48</v>
       </c>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
     </row>
-    <row r="10" spans="1:22" ht="36" x14ac:dyDescent="1.2">
+    <row r="10" spans="1:22" ht="31" x14ac:dyDescent="0.35">
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="1.05">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="51" t="s">
+      <c r="F11" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="1.05">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="49"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
       <c r="F12" s="2">
         <v>1</v>
       </c>
@@ -2226,1671 +2234,1677 @@
       <c r="K12" s="8">
         <v>6</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="26">
         <v>7</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-    </row>
-    <row r="13" spans="1:22" ht="34" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A13" s="31">
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+    </row>
+    <row r="13" spans="1:22" ht="34" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
         <v>1</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="13">
         <v>1</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="13">
         <v>1</v>
       </c>
-      <c r="G13" s="18">
-        <v>0</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="1.05">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="17" t="s">
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+    </row>
+    <row r="14" spans="1:22" ht="27" x14ac:dyDescent="0.3">
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="13">
         <v>1</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="13">
         <v>1</v>
       </c>
-      <c r="G14" s="18">
-        <v>0</v>
-      </c>
-      <c r="H14" s="18">
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <v>0</v>
-      </c>
-      <c r="K14" s="19">
-        <v>0</v>
-      </c>
-      <c r="L14" s="20">
-        <v>0</v>
-      </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-    </row>
-    <row r="15" spans="1:22" ht="31" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="21" t="s">
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+    </row>
+    <row r="15" spans="1:22" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="17">
         <v>1</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="17">
         <v>1</v>
       </c>
-      <c r="G15" s="22">
-        <v>0</v>
-      </c>
-      <c r="H15" s="22">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22">
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <v>0</v>
-      </c>
-      <c r="K15" s="23">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20">
-        <v>0</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="1.05">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="24" t="s">
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18">
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+    </row>
+    <row r="16" spans="1:22" ht="27" x14ac:dyDescent="0.3">
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="15">
         <v>4</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="15">
         <v>4</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="15">
         <v>4</v>
       </c>
-      <c r="H16" s="20">
-        <v>0</v>
-      </c>
-      <c r="I16" s="20">
-        <v>0</v>
-      </c>
-      <c r="J16" s="20">
-        <v>0</v>
-      </c>
-      <c r="K16" s="25">
-        <v>0</v>
-      </c>
-      <c r="L16" s="20">
-        <v>0</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="24" t="s">
+      <c r="H16" s="15">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
+        <v>0</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+    </row>
+    <row r="17" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="15">
         <v>1</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="15">
         <v>1</v>
       </c>
-      <c r="G17" s="20">
-        <v>0</v>
-      </c>
-      <c r="H17" s="20">
-        <v>0</v>
-      </c>
-      <c r="I17" s="20">
-        <v>0</v>
-      </c>
-      <c r="J17" s="20">
-        <v>0</v>
-      </c>
-      <c r="K17" s="25">
-        <v>0</v>
-      </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="24" t="s">
+      <c r="G17" s="15">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
+        <v>0</v>
+      </c>
+      <c r="J17" s="15">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+    </row>
+    <row r="18" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="20">
-        <v>2</v>
-      </c>
-      <c r="F18" s="20">
-        <v>2</v>
-      </c>
-      <c r="G18" s="20">
-        <v>0</v>
-      </c>
-      <c r="H18" s="20">
-        <v>0</v>
-      </c>
-      <c r="I18" s="20">
-        <v>0</v>
-      </c>
-      <c r="J18" s="20">
-        <v>0</v>
-      </c>
-      <c r="K18" s="25">
-        <v>0</v>
-      </c>
-      <c r="L18" s="20">
-        <v>0</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="30" t="s">
+      <c r="E18" s="15">
+        <v>2</v>
+      </c>
+      <c r="F18" s="15">
+        <v>2</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>0</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20">
+        <v>0</v>
+      </c>
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+    </row>
+    <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="20">
-        <v>2</v>
-      </c>
-      <c r="F19" s="20">
-        <v>2</v>
-      </c>
-      <c r="G19" s="20">
-        <v>2</v>
-      </c>
-      <c r="H19" s="20">
-        <v>0</v>
-      </c>
-      <c r="I19" s="20">
-        <v>0</v>
-      </c>
-      <c r="J19" s="20">
-        <v>0</v>
-      </c>
-      <c r="K19" s="25">
-        <v>0</v>
-      </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="30" t="s">
+      <c r="E19" s="15">
+        <v>2</v>
+      </c>
+      <c r="F19" s="15">
+        <v>2</v>
+      </c>
+      <c r="G19" s="15">
+        <v>2</v>
+      </c>
+      <c r="H19" s="15">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="15">
         <v>3</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="15">
         <v>3</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="15">
         <v>3</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="15">
         <v>3</v>
       </c>
-      <c r="I20" s="20">
-        <v>0</v>
-      </c>
-      <c r="J20" s="20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="25">
-        <v>0</v>
-      </c>
-      <c r="L20" s="20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="30" t="s">
+      <c r="I20" s="15">
+        <v>0</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0</v>
+      </c>
+      <c r="K20" s="20">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="20">
-        <v>2</v>
-      </c>
-      <c r="F21" s="20">
-        <v>2</v>
-      </c>
-      <c r="G21" s="20">
-        <v>2</v>
-      </c>
-      <c r="H21" s="20">
-        <v>0</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0</v>
-      </c>
-      <c r="K21" s="25">
-        <v>0</v>
-      </c>
-      <c r="L21" s="20">
-        <v>0</v>
-      </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="30" t="s">
+      <c r="E21" s="15">
+        <v>2</v>
+      </c>
+      <c r="F21" s="15">
+        <v>2</v>
+      </c>
+      <c r="G21" s="15">
+        <v>2</v>
+      </c>
+      <c r="H21" s="15">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0</v>
+      </c>
+      <c r="K21" s="20">
+        <v>0</v>
+      </c>
+      <c r="L21" s="15">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="20">
-        <v>2</v>
-      </c>
-      <c r="F22" s="20">
-        <v>2</v>
-      </c>
-      <c r="G22" s="20">
-        <v>2</v>
-      </c>
-      <c r="H22" s="20">
-        <v>0</v>
-      </c>
-      <c r="I22" s="20">
-        <v>0</v>
-      </c>
-      <c r="J22" s="20">
-        <v>0</v>
-      </c>
-      <c r="K22" s="25">
-        <v>0</v>
-      </c>
-      <c r="L22" s="20">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="30" t="s">
+      <c r="E22" s="15">
+        <v>2</v>
+      </c>
+      <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
+        <v>0</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0</v>
+      </c>
+      <c r="K22" s="20">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="15">
         <v>3</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="15">
         <v>3</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="15">
         <v>3</v>
       </c>
-      <c r="H23" s="20">
-        <v>0</v>
-      </c>
-      <c r="I23" s="20">
-        <v>0</v>
-      </c>
-      <c r="J23" s="20">
-        <v>0</v>
-      </c>
-      <c r="K23" s="25">
-        <v>0</v>
-      </c>
-      <c r="L23" s="20">
-        <v>0</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="30" t="s">
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
+        <v>0</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="15">
         <v>6</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="15">
         <v>6</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="15">
         <v>6</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="15">
         <v>6</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="15">
         <v>6</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="15">
         <v>6</v>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="20">
         <v>6</v>
       </c>
-      <c r="L24" s="20">
-        <v>0</v>
-      </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="30" t="s">
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="15">
         <v>1</v>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="15">
         <v>1</v>
       </c>
-      <c r="G25" s="20">
-        <v>0</v>
-      </c>
-      <c r="H25" s="20">
-        <v>0</v>
-      </c>
-      <c r="I25" s="20">
-        <v>0</v>
-      </c>
-      <c r="J25" s="20">
-        <v>0</v>
-      </c>
-      <c r="K25" s="25">
-        <v>0</v>
-      </c>
-      <c r="L25" s="20">
-        <v>0</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="30" t="s">
+      <c r="G25" s="15">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
+        <v>0</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0</v>
+      </c>
+      <c r="K25" s="20">
+        <v>0</v>
+      </c>
+      <c r="L25" s="15">
+        <v>0</v>
+      </c>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="20">
-        <v>2</v>
-      </c>
-      <c r="F26" s="20">
-        <v>2</v>
-      </c>
-      <c r="G26" s="20">
-        <v>2</v>
-      </c>
-      <c r="H26" s="20">
-        <v>0</v>
-      </c>
-      <c r="I26" s="20">
-        <v>0</v>
-      </c>
-      <c r="J26" s="20">
-        <v>0</v>
-      </c>
-      <c r="K26" s="25">
-        <v>0</v>
-      </c>
-      <c r="L26" s="20">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="30" t="s">
+      <c r="E26" s="15">
+        <v>2</v>
+      </c>
+      <c r="F26" s="15">
+        <v>2</v>
+      </c>
+      <c r="G26" s="15">
+        <v>2</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20">
+        <v>0</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="20">
-        <v>2</v>
-      </c>
-      <c r="F27" s="20">
-        <v>2</v>
-      </c>
-      <c r="G27" s="20">
-        <v>2</v>
-      </c>
-      <c r="H27" s="20">
-        <v>2</v>
-      </c>
-      <c r="I27" s="20">
-        <v>2</v>
-      </c>
-      <c r="J27" s="20">
-        <v>2</v>
-      </c>
-      <c r="K27" s="25">
-        <v>2</v>
-      </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A28" s="32"/>
-      <c r="B28" s="31" t="s">
+      <c r="E27" s="15">
+        <v>2</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>2</v>
+      </c>
+      <c r="I27" s="15">
+        <v>2</v>
+      </c>
+      <c r="J27" s="15">
+        <v>2</v>
+      </c>
+      <c r="K27" s="20">
+        <v>2</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14" ht="58" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="44"/>
+      <c r="B28" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="15">
         <v>1</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="15">
         <v>1</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="H28" s="20">
-        <v>0</v>
-      </c>
-      <c r="I28" s="20">
-        <v>0</v>
-      </c>
-      <c r="J28" s="20">
-        <v>0</v>
-      </c>
-      <c r="K28" s="20">
-        <v>0</v>
-      </c>
-      <c r="L28" s="20">
-        <v>0</v>
-      </c>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-    </row>
-    <row r="29" spans="1:14" ht="34" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="24" t="s">
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0</v>
+      </c>
+      <c r="J28" s="15">
+        <v>0</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
+        <v>0</v>
+      </c>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+    </row>
+    <row r="29" spans="1:14" ht="34" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="15">
         <v>1</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="20">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20">
-        <v>0</v>
-      </c>
-      <c r="I29" s="20">
-        <v>0</v>
-      </c>
-      <c r="J29" s="20">
-        <v>0</v>
-      </c>
-      <c r="K29" s="20">
-        <v>0</v>
-      </c>
-      <c r="L29" s="20">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-    </row>
-    <row r="30" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="24" t="s">
+      <c r="G29" s="15">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>0</v>
+      </c>
+      <c r="J29" s="15">
+        <v>0</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <v>0</v>
+      </c>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
+    </row>
+    <row r="30" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="15">
         <v>3</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="15">
         <v>3</v>
       </c>
-      <c r="G30" s="20">
-        <v>0</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
-      <c r="J30" s="20">
-        <v>0</v>
-      </c>
-      <c r="K30" s="20">
-        <v>0</v>
-      </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-    </row>
-    <row r="31" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="24" t="s">
+      <c r="G30" s="15">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
+        <v>0</v>
+      </c>
+      <c r="J30" s="15">
+        <v>0</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
+    </row>
+    <row r="31" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="15">
         <v>3</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="15">
         <v>3</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="15">
         <v>3</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="15">
         <v>3</v>
       </c>
-      <c r="I31" s="20">
-        <v>0</v>
-      </c>
-      <c r="J31" s="20">
-        <v>0</v>
-      </c>
-      <c r="K31" s="20">
-        <v>0</v>
-      </c>
-      <c r="L31" s="20">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-    </row>
-    <row r="32" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="24" t="s">
+      <c r="I31" s="15">
+        <v>0</v>
+      </c>
+      <c r="J31" s="15">
+        <v>0</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
+    </row>
+    <row r="32" spans="1:14" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="44"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="15">
         <v>1</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="15">
         <v>1</v>
       </c>
-      <c r="G32" s="20">
-        <v>0</v>
-      </c>
-      <c r="H32" s="20">
-        <v>0</v>
-      </c>
-      <c r="I32" s="20">
-        <v>0</v>
-      </c>
-      <c r="J32" s="20">
-        <v>0</v>
-      </c>
-      <c r="K32" s="20">
-        <v>0</v>
-      </c>
-      <c r="L32" s="20">
-        <v>0</v>
-      </c>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-    </row>
-    <row r="33" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="24" t="s">
+      <c r="G32" s="15">
+        <v>0</v>
+      </c>
+      <c r="H32" s="15">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0</v>
+      </c>
+      <c r="J32" s="15">
+        <v>0</v>
+      </c>
+      <c r="K32" s="15">
+        <v>0</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0</v>
+      </c>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+    </row>
+    <row r="33" spans="1:14" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="15">
         <v>3</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="15">
         <v>3</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="15">
         <v>3</v>
       </c>
-      <c r="H33" s="20">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-      <c r="J33" s="20">
-        <v>0</v>
-      </c>
-      <c r="K33" s="20">
-        <v>0</v>
-      </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-    </row>
-    <row r="34" spans="1:14" ht="38" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="24" t="s">
+      <c r="H33" s="15">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15">
+        <v>0</v>
+      </c>
+      <c r="J33" s="15">
+        <v>0</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0</v>
+      </c>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+    </row>
+    <row r="34" spans="1:14" ht="38" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="15">
         <v>3</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="10">
         <v>3</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="15">
         <v>3</v>
       </c>
-      <c r="H34" s="20">
-        <v>0</v>
-      </c>
-      <c r="I34" s="20">
-        <v>0</v>
-      </c>
-      <c r="J34" s="20">
-        <v>0</v>
-      </c>
-      <c r="K34" s="20">
-        <v>0</v>
-      </c>
-      <c r="L34" s="20">
-        <v>0</v>
-      </c>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-    </row>
-    <row r="35" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="29" t="s">
+      <c r="H34" s="15">
+        <v>0</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0</v>
+      </c>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+    </row>
+    <row r="35" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="15">
         <v>1</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="15">
         <v>1</v>
       </c>
-      <c r="G35" s="20">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20">
-        <v>0</v>
-      </c>
-      <c r="I35" s="20">
-        <v>0</v>
-      </c>
-      <c r="J35" s="20">
-        <v>0</v>
-      </c>
-      <c r="K35" s="20">
-        <v>0</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-    </row>
-    <row r="36" spans="1:14" ht="52" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="29" t="s">
+      <c r="G35" s="15">
+        <v>0</v>
+      </c>
+      <c r="H35" s="15">
+        <v>0</v>
+      </c>
+      <c r="I35" s="15">
+        <v>0</v>
+      </c>
+      <c r="J35" s="15">
+        <v>0</v>
+      </c>
+      <c r="K35" s="15">
+        <v>0</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0</v>
+      </c>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+    </row>
+    <row r="36" spans="1:14" ht="52" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="20">
-        <v>2</v>
-      </c>
-      <c r="F36" s="20">
-        <v>2</v>
-      </c>
-      <c r="G36" s="20">
-        <v>2</v>
-      </c>
-      <c r="H36" s="20">
-        <v>0</v>
-      </c>
-      <c r="I36" s="20">
-        <v>0</v>
-      </c>
-      <c r="J36" s="20">
-        <v>0</v>
-      </c>
-      <c r="K36" s="20">
-        <v>0</v>
-      </c>
-      <c r="L36" s="20">
-        <v>0</v>
-      </c>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-    </row>
-    <row r="37" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="24" t="s">
+      <c r="E36" s="15">
+        <v>2</v>
+      </c>
+      <c r="F36" s="15">
+        <v>2</v>
+      </c>
+      <c r="G36" s="15">
+        <v>2</v>
+      </c>
+      <c r="H36" s="15">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15">
+        <v>0</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0</v>
+      </c>
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+    </row>
+    <row r="37" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="15">
         <v>3</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="15">
         <v>3</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="15">
         <v>3</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="15">
         <v>3</v>
       </c>
-      <c r="I37" s="20">
-        <v>0</v>
-      </c>
-      <c r="J37" s="20">
-        <v>0</v>
-      </c>
-      <c r="K37" s="20">
-        <v>0</v>
-      </c>
-      <c r="L37" s="20">
-        <v>0</v>
-      </c>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-    </row>
-    <row r="38" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A38" s="32"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="24" t="s">
+      <c r="I37" s="15">
+        <v>0</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0</v>
+      </c>
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
+    </row>
+    <row r="38" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="20">
-        <v>2</v>
-      </c>
-      <c r="F38" s="20">
-        <v>2</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20">
-        <v>0</v>
-      </c>
-      <c r="I38" s="20">
-        <v>0</v>
-      </c>
-      <c r="J38" s="20">
-        <v>0</v>
-      </c>
-      <c r="K38" s="20">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-    </row>
-    <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="29" t="s">
+      <c r="E38" s="15">
+        <v>2</v>
+      </c>
+      <c r="F38" s="15">
+        <v>2</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0</v>
+      </c>
+      <c r="H38" s="15">
+        <v>0</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0</v>
+      </c>
+      <c r="K38" s="15">
+        <v>0</v>
+      </c>
+      <c r="L38" s="15">
+        <v>0</v>
+      </c>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
+    </row>
+    <row r="39" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="20">
-        <v>2</v>
-      </c>
-      <c r="F39" s="20">
-        <v>2</v>
-      </c>
-      <c r="G39" s="20">
-        <v>2</v>
-      </c>
-      <c r="H39" s="20">
-        <v>0</v>
-      </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>0</v>
-      </c>
-      <c r="K39" s="20">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-    </row>
-    <row r="40" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="29" t="s">
+      <c r="E39" s="15">
+        <v>2</v>
+      </c>
+      <c r="F39" s="15">
+        <v>2</v>
+      </c>
+      <c r="G39" s="15">
+        <v>2</v>
+      </c>
+      <c r="H39" s="15">
+        <v>0</v>
+      </c>
+      <c r="I39" s="15">
+        <v>0</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0</v>
+      </c>
+      <c r="K39" s="15">
+        <v>0</v>
+      </c>
+      <c r="L39" s="15">
+        <v>0</v>
+      </c>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42"/>
+    </row>
+    <row r="40" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D40" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="15">
         <v>3</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="15">
         <v>3</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="15">
         <v>3</v>
       </c>
-      <c r="H40" s="20">
-        <v>0</v>
-      </c>
-      <c r="I40" s="20">
-        <v>0</v>
-      </c>
-      <c r="J40" s="20">
-        <v>0</v>
-      </c>
-      <c r="K40" s="20">
-        <v>0</v>
-      </c>
-      <c r="L40" s="20">
-        <v>0</v>
-      </c>
-      <c r="M40" s="37"/>
-      <c r="N40" s="35"/>
-    </row>
-    <row r="41" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A41" s="32"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="30" t="s">
+      <c r="H40" s="15">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0</v>
+      </c>
+      <c r="L40" s="15">
+        <v>0</v>
+      </c>
+      <c r="M40" s="41"/>
+      <c r="N40" s="42"/>
+    </row>
+    <row r="41" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="44"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="25">
         <v>8</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="25">
         <v>8</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="25">
         <v>8</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="25">
         <v>8</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="25">
         <v>8</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="25">
         <v>8</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="25">
         <v>8</v>
       </c>
-      <c r="L41" s="34">
-        <v>0</v>
-      </c>
-      <c r="M41" s="37"/>
-      <c r="N41" s="35"/>
-    </row>
-    <row r="42" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A42" s="32"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="30" t="s">
+      <c r="L41" s="25">
+        <v>0</v>
+      </c>
+      <c r="M41" s="41"/>
+      <c r="N41" s="42"/>
+    </row>
+    <row r="42" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="44"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="25">
         <v>1</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="25">
         <v>1</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="25">
         <v>1</v>
       </c>
-      <c r="H42" s="34">
-        <v>0</v>
-      </c>
-      <c r="I42" s="34">
-        <v>0</v>
-      </c>
-      <c r="J42" s="34">
-        <v>0</v>
-      </c>
-      <c r="K42" s="34">
-        <v>0</v>
-      </c>
-      <c r="L42" s="34">
-        <v>0</v>
-      </c>
-      <c r="M42" s="37"/>
-      <c r="N42" s="35"/>
-    </row>
-    <row r="43" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="30" t="s">
+      <c r="H42" s="25">
+        <v>0</v>
+      </c>
+      <c r="I42" s="25">
+        <v>0</v>
+      </c>
+      <c r="J42" s="25">
+        <v>0</v>
+      </c>
+      <c r="K42" s="25">
+        <v>0</v>
+      </c>
+      <c r="L42" s="25">
+        <v>0</v>
+      </c>
+      <c r="M42" s="41"/>
+      <c r="N42" s="42"/>
+    </row>
+    <row r="43" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="34">
-        <v>2</v>
-      </c>
-      <c r="F43" s="34">
-        <v>2</v>
-      </c>
-      <c r="G43" s="34">
-        <v>2</v>
-      </c>
-      <c r="H43" s="34">
-        <v>0</v>
-      </c>
-      <c r="I43" s="34">
-        <v>0</v>
-      </c>
-      <c r="J43" s="34">
-        <v>0</v>
-      </c>
-      <c r="K43" s="34">
-        <v>0</v>
-      </c>
-      <c r="L43" s="34">
-        <v>0</v>
-      </c>
-      <c r="M43" s="37"/>
-      <c r="N43" s="35"/>
-    </row>
-    <row r="44" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A44" s="32"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="30" t="s">
+      <c r="E43" s="25">
+        <v>2</v>
+      </c>
+      <c r="F43" s="25">
+        <v>2</v>
+      </c>
+      <c r="G43" s="25">
+        <v>2</v>
+      </c>
+      <c r="H43" s="25">
+        <v>0</v>
+      </c>
+      <c r="I43" s="25">
+        <v>0</v>
+      </c>
+      <c r="J43" s="25">
+        <v>0</v>
+      </c>
+      <c r="K43" s="25">
+        <v>0</v>
+      </c>
+      <c r="L43" s="25">
+        <v>0</v>
+      </c>
+      <c r="M43" s="41"/>
+      <c r="N43" s="42"/>
+    </row>
+    <row r="44" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="44"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="34">
-        <v>2</v>
-      </c>
-      <c r="F44" s="34">
-        <v>2</v>
-      </c>
-      <c r="G44" s="34">
-        <v>2</v>
-      </c>
-      <c r="H44" s="34">
-        <v>2</v>
-      </c>
-      <c r="I44" s="34">
-        <v>2</v>
-      </c>
-      <c r="J44" s="34">
-        <v>2</v>
-      </c>
-      <c r="K44" s="34">
-        <v>2</v>
-      </c>
-      <c r="L44" s="34">
-        <v>0</v>
-      </c>
-      <c r="M44" s="37"/>
-      <c r="N44" s="35"/>
-    </row>
-    <row r="45" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A45" s="32"/>
-      <c r="B45" s="31" t="s">
+      <c r="E44" s="25">
+        <v>2</v>
+      </c>
+      <c r="F44" s="25">
+        <v>2</v>
+      </c>
+      <c r="G44" s="25">
+        <v>2</v>
+      </c>
+      <c r="H44" s="25">
+        <v>2</v>
+      </c>
+      <c r="I44" s="25">
+        <v>2</v>
+      </c>
+      <c r="J44" s="25">
+        <v>2</v>
+      </c>
+      <c r="K44" s="25">
+        <v>2</v>
+      </c>
+      <c r="L44" s="25">
+        <v>0</v>
+      </c>
+      <c r="M44" s="41"/>
+      <c r="N44" s="42"/>
+    </row>
+    <row r="45" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="44"/>
+      <c r="B45" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="41" t="s">
+      <c r="D45" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="39">
+      <c r="E45" s="28">
         <v>3</v>
       </c>
-      <c r="F45" s="39">
+      <c r="F45" s="28">
         <v>3</v>
       </c>
-      <c r="G45" s="39">
+      <c r="G45" s="28">
         <v>3</v>
       </c>
-      <c r="H45" s="39">
-        <v>0</v>
-      </c>
-      <c r="I45" s="39">
-        <v>0</v>
-      </c>
-      <c r="J45" s="39">
-        <v>0</v>
-      </c>
-      <c r="K45" s="42">
-        <v>0</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0</v>
-      </c>
-      <c r="M45" s="37"/>
-      <c r="N45" s="35"/>
-    </row>
-    <row r="46" spans="1:14" ht="43" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="43" t="s">
+      <c r="H45" s="28">
+        <v>0</v>
+      </c>
+      <c r="I45" s="28">
+        <v>0</v>
+      </c>
+      <c r="J45" s="28">
+        <v>0</v>
+      </c>
+      <c r="K45" s="31">
+        <v>0</v>
+      </c>
+      <c r="L45" s="15">
+        <v>0</v>
+      </c>
+      <c r="M45" s="41"/>
+      <c r="N45" s="42"/>
+    </row>
+    <row r="46" spans="1:14" ht="43" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="41" t="s">
+      <c r="D46" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="13">
         <v>3</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="13">
         <v>3</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="13">
         <v>3</v>
       </c>
-      <c r="H46" s="18">
-        <v>0</v>
-      </c>
-      <c r="I46" s="18">
-        <v>0</v>
-      </c>
-      <c r="J46" s="18">
-        <v>0</v>
-      </c>
-      <c r="K46" s="19">
-        <v>0</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0</v>
-      </c>
-      <c r="M46" s="37"/>
-      <c r="N46" s="35"/>
-    </row>
-    <row r="47" spans="1:14" ht="30.5" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="43" t="s">
+      <c r="H46" s="13">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13">
+        <v>0</v>
+      </c>
+      <c r="K46" s="14">
+        <v>0</v>
+      </c>
+      <c r="L46" s="15">
+        <v>0</v>
+      </c>
+      <c r="M46" s="41"/>
+      <c r="N46" s="42"/>
+    </row>
+    <row r="47" spans="1:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="13">
         <v>1</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="13">
         <v>1</v>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="13">
         <v>1</v>
       </c>
-      <c r="H47" s="18">
-        <v>0</v>
-      </c>
-      <c r="I47" s="18">
-        <v>0</v>
-      </c>
-      <c r="J47" s="18">
-        <v>0</v>
-      </c>
-      <c r="K47" s="19">
-        <v>0</v>
-      </c>
-      <c r="L47" s="20">
-        <v>0</v>
-      </c>
-      <c r="M47" s="37"/>
-      <c r="N47" s="35"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="1.05">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="43" t="s">
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13">
+        <v>0</v>
+      </c>
+      <c r="K47" s="14">
+        <v>0</v>
+      </c>
+      <c r="L47" s="15">
+        <v>0</v>
+      </c>
+      <c r="M47" s="41"/>
+      <c r="N47" s="42"/>
+    </row>
+    <row r="48" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="13">
         <v>1</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="13">
         <v>1</v>
       </c>
-      <c r="G48" s="18">
+      <c r="G48" s="13">
         <v>1</v>
       </c>
-      <c r="H48" s="18">
-        <v>0</v>
-      </c>
-      <c r="I48" s="18">
-        <v>0</v>
-      </c>
-      <c r="J48" s="18">
-        <v>0</v>
-      </c>
-      <c r="K48" s="19">
-        <v>0</v>
-      </c>
-      <c r="L48" s="20">
-        <v>0</v>
-      </c>
-      <c r="M48" s="37"/>
-      <c r="N48" s="35"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="44" t="s">
+      <c r="H48" s="13">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13">
+        <v>0</v>
+      </c>
+      <c r="K48" s="14">
+        <v>0</v>
+      </c>
+      <c r="L48" s="15">
+        <v>0</v>
+      </c>
+      <c r="M48" s="41"/>
+      <c r="N48" s="42"/>
+    </row>
+    <row r="49" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="17">
         <v>3</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="17">
         <v>3</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="17">
         <v>3</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="17">
         <v>3</v>
       </c>
-      <c r="I49" s="22">
+      <c r="I49" s="17">
         <f>--H447</f>
         <v>0</v>
       </c>
-      <c r="J49" s="22">
-        <v>0</v>
-      </c>
-      <c r="K49" s="23">
-        <v>0</v>
-      </c>
-      <c r="L49" s="20">
-        <v>0</v>
-      </c>
-      <c r="M49" s="37"/>
-      <c r="N49" s="35"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="45" t="s">
+      <c r="J49" s="17">
+        <v>0</v>
+      </c>
+      <c r="K49" s="18">
+        <v>0</v>
+      </c>
+      <c r="L49" s="15">
+        <v>0</v>
+      </c>
+      <c r="M49" s="41"/>
+      <c r="N49" s="42"/>
+    </row>
+    <row r="50" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="46" t="s">
+      <c r="D50" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="47">
+      <c r="E50" s="36">
         <v>4</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="17">
         <v>4</v>
       </c>
-      <c r="G50" s="22">
+      <c r="G50" s="17">
         <v>4</v>
       </c>
-      <c r="H50" s="22">
-        <v>0</v>
-      </c>
-      <c r="I50" s="22">
-        <v>0</v>
-      </c>
-      <c r="J50" s="22">
-        <v>0</v>
-      </c>
-      <c r="K50" s="23">
-        <v>0</v>
-      </c>
-      <c r="L50" s="20">
-        <v>0</v>
-      </c>
-      <c r="M50" s="37"/>
-      <c r="N50" s="35"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
+      <c r="H50" s="17">
+        <v>0</v>
+      </c>
+      <c r="I50" s="17">
+        <v>0</v>
+      </c>
+      <c r="J50" s="17">
+        <v>0</v>
+      </c>
+      <c r="K50" s="18">
+        <v>0</v>
+      </c>
+      <c r="L50" s="15">
+        <v>0</v>
+      </c>
+      <c r="M50" s="41"/>
+      <c r="N50" s="42"/>
+    </row>
+    <row r="51" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+      <c r="A51" s="44"/>
+      <c r="B51" s="44"/>
       <c r="C51" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E51" s="26">
-        <v>2</v>
-      </c>
-      <c r="F51" s="20">
-        <v>2</v>
-      </c>
-      <c r="G51" s="20">
-        <v>2</v>
-      </c>
-      <c r="H51" s="20">
-        <v>0</v>
-      </c>
-      <c r="I51" s="20">
-        <v>0</v>
-      </c>
-      <c r="J51" s="20">
-        <v>0</v>
-      </c>
-      <c r="K51" s="20">
-        <v>0</v>
-      </c>
-      <c r="L51" s="20">
-        <v>0</v>
-      </c>
-      <c r="M51" s="50"/>
-      <c r="N51" s="9"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="30" t="s">
+      <c r="E51" s="21">
+        <v>2</v>
+      </c>
+      <c r="F51" s="15">
+        <v>2</v>
+      </c>
+      <c r="G51" s="15">
+        <v>2</v>
+      </c>
+      <c r="H51" s="15">
+        <v>0</v>
+      </c>
+      <c r="I51" s="15">
+        <v>0</v>
+      </c>
+      <c r="J51" s="15">
+        <v>0</v>
+      </c>
+      <c r="K51" s="15">
+        <v>0</v>
+      </c>
+      <c r="L51" s="15">
+        <v>0</v>
+      </c>
+      <c r="M51" s="52"/>
+      <c r="N51" s="53"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="44"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="30" t="s">
+      <c r="D52" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="52">
+      <c r="E52" s="38">
         <v>3</v>
       </c>
-      <c r="F52" s="52">
+      <c r="F52" s="38">
         <v>3</v>
       </c>
-      <c r="G52" s="52">
-        <v>0</v>
-      </c>
-      <c r="H52" s="52">
-        <v>0</v>
-      </c>
-      <c r="I52" s="52">
-        <v>0</v>
-      </c>
-      <c r="J52" s="52">
-        <v>0</v>
-      </c>
-      <c r="K52" s="52">
-        <v>0</v>
-      </c>
-      <c r="L52" s="52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="30" t="s">
+      <c r="G52" s="38">
+        <v>0</v>
+      </c>
+      <c r="H52" s="38">
+        <v>0</v>
+      </c>
+      <c r="I52" s="38">
+        <v>0</v>
+      </c>
+      <c r="J52" s="38">
+        <v>0</v>
+      </c>
+      <c r="K52" s="38">
+        <v>0</v>
+      </c>
+      <c r="L52" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="30" t="s">
+      <c r="D53" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E53" s="52">
+      <c r="E53" s="38">
         <v>8</v>
       </c>
-      <c r="F53" s="52">
+      <c r="F53" s="38">
         <v>8</v>
       </c>
-      <c r="G53" s="52">
+      <c r="G53" s="38">
         <v>8</v>
       </c>
-      <c r="H53" s="52">
+      <c r="H53" s="38">
         <v>8</v>
       </c>
-      <c r="I53" s="52">
+      <c r="I53" s="38">
         <v>8</v>
       </c>
-      <c r="J53" s="52">
+      <c r="J53" s="38">
         <v>8</v>
       </c>
-      <c r="K53" s="52">
+      <c r="K53" s="38">
         <v>8</v>
       </c>
-      <c r="L53" s="52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A54" s="32"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="30" t="s">
+      <c r="L53" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="30" t="s">
+      <c r="D54" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="52">
+      <c r="E54" s="38">
         <v>1</v>
       </c>
-      <c r="F54" s="52">
+      <c r="F54" s="38">
         <v>1</v>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="38">
         <v>1</v>
       </c>
-      <c r="H54" s="52">
-        <v>0</v>
-      </c>
-      <c r="I54" s="52">
-        <v>0</v>
-      </c>
-      <c r="J54" s="52">
-        <v>0</v>
-      </c>
-      <c r="K54" s="52">
-        <v>0</v>
-      </c>
-      <c r="L54" s="52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A55" s="32"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="30" t="s">
+      <c r="H54" s="38">
+        <v>0</v>
+      </c>
+      <c r="I54" s="38">
+        <v>0</v>
+      </c>
+      <c r="J54" s="38">
+        <v>0</v>
+      </c>
+      <c r="K54" s="38">
+        <v>0</v>
+      </c>
+      <c r="L54" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E55" s="52">
-        <v>2</v>
-      </c>
-      <c r="F55" s="52">
-        <v>2</v>
-      </c>
-      <c r="G55" s="52">
-        <v>2</v>
-      </c>
-      <c r="H55" s="52">
-        <v>0</v>
-      </c>
-      <c r="I55" s="52">
-        <v>0</v>
-      </c>
-      <c r="J55" s="52">
-        <v>0</v>
-      </c>
-      <c r="K55" s="52">
-        <v>0</v>
-      </c>
-      <c r="L55" s="52">
+      <c r="E55" s="38">
+        <v>2</v>
+      </c>
+      <c r="F55" s="38">
+        <v>2</v>
+      </c>
+      <c r="G55" s="38">
+        <v>2</v>
+      </c>
+      <c r="H55" s="38">
+        <v>0</v>
+      </c>
+      <c r="I55" s="38">
+        <v>0</v>
+      </c>
+      <c r="J55" s="38">
+        <v>0</v>
+      </c>
+      <c r="K55" s="38">
+        <v>0</v>
+      </c>
+      <c r="L55" s="38">
         <v>0</v>
       </c>
       <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="1.05">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="30" t="s">
+    <row r="56" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+      <c r="A56" s="45"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E56" s="52">
-        <v>2</v>
-      </c>
-      <c r="F56" s="52">
-        <v>2</v>
-      </c>
-      <c r="G56" s="52">
-        <v>2</v>
-      </c>
-      <c r="H56" s="38">
-        <v>0</v>
-      </c>
-      <c r="I56" s="38">
-        <v>0</v>
-      </c>
-      <c r="J56" s="38">
-        <v>0</v>
-      </c>
-      <c r="K56" s="52">
-        <v>0</v>
-      </c>
-      <c r="L56" s="52">
+      <c r="E56" s="38">
+        <v>2</v>
+      </c>
+      <c r="F56" s="38">
+        <v>2</v>
+      </c>
+      <c r="G56" s="38">
+        <v>2</v>
+      </c>
+      <c r="H56" s="27">
+        <v>0</v>
+      </c>
+      <c r="I56" s="27">
+        <v>0</v>
+      </c>
+      <c r="J56" s="27">
+        <v>0</v>
+      </c>
+      <c r="K56" s="38">
+        <v>0</v>
+      </c>
+      <c r="L56" s="38">
         <v>0</v>
       </c>
       <c r="M56"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="1.05">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="53">
-        <f>SUM(E13:E56)</f>
+      <c r="D57" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57" s="39">
+        <f t="shared" ref="E57:K57" si="0">SUM(E13:E56)</f>
         <v>107</v>
       </c>
       <c r="F57" s="1">
-        <f>SUM(F13:F56)</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="G57" s="1">
-        <f>SUM(G13:G56)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="H57" s="1">
-        <f>SUM(H13:H56)</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="I57" s="1">
-        <f>SUM(I13:I56)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="J57" s="1">
-        <f>SUM(J13:J56)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="K57" s="1">
-        <f>SUM(K13:K56)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
       </c>
-      <c r="N57" s="48"/>
-      <c r="O57" s="49"/>
-      <c r="P57" s="49"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="1.05">
+      <c r="N57" s="37"/>
+      <c r="O57" s="37"/>
+      <c r="P57" s="37"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="N58" s="48"/>
-      <c r="O58" s="49"/>
-      <c r="P58" s="49"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="1.05">
+      <c r="D58" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" s="9">
+        <v>166</v>
+      </c>
+      <c r="N58" s="37"/>
+      <c r="O58" s="37"/>
+      <c r="P58" s="37"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
-      <c r="N59" s="48"/>
-      <c r="O59" s="49"/>
-      <c r="P59" s="49"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="1.05">
+      <c r="N59" s="37"/>
+      <c r="O59" s="37"/>
+      <c r="P59" s="37"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
-      <c r="N60" s="48"/>
-      <c r="O60" s="49"/>
-      <c r="P60" s="49"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="1.05">
+      <c r="N60" s="37"/>
+      <c r="O60" s="37"/>
+      <c r="P60" s="37"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="I61"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="1.05">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
@@ -3900,7 +3914,7 @@
       <c r="H62" s="7"/>
       <c r="I62"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="1.05">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
@@ -3910,7 +3924,7 @@
       <c r="H63" s="7"/>
       <c r="I63"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="1.05">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -3920,7 +3934,7 @@
       <c r="H64" s="7"/>
       <c r="I64"/>
     </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="1.05">
+    <row r="65" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -3930,10 +3944,10 @@
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
     </row>
-    <row r="66" spans="2:28" ht="27" customHeight="1" x14ac:dyDescent="1.05"/>
-    <row r="75" spans="2:28" ht="26" customHeight="1" x14ac:dyDescent="1.05"/>
-    <row r="76" spans="2:28" ht="26" customHeight="1" x14ac:dyDescent="1.05"/>
-    <row r="77" spans="2:28" x14ac:dyDescent="1.05">
+    <row r="66" spans="2:28" ht="27" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="2:28" ht="26" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="2:28" ht="26" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.3">
       <c r="Q77" s="6"/>
       <c r="R77" s="6"/>
       <c r="S77" s="6"/>
@@ -3944,7 +3958,7 @@
       <c r="X77" s="6"/>
       <c r="Y77" s="6"/>
     </row>
-    <row r="78" spans="2:28" x14ac:dyDescent="1.05">
+    <row r="78" spans="2:28" x14ac:dyDescent="0.3">
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
       <c r="S78" s="6"/>
@@ -3955,7 +3969,7 @@
       <c r="X78" s="6"/>
       <c r="Y78" s="6"/>
     </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="1.05">
+    <row r="79" spans="2:28" x14ac:dyDescent="0.3">
       <c r="Q79" s="6"/>
       <c r="R79" s="6"/>
       <c r="S79" s="6"/>
@@ -3966,7 +3980,7 @@
       <c r="X79" s="6"/>
       <c r="Y79" s="6"/>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="1.05">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.3">
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
       <c r="S80" s="6"/>
@@ -3980,7 +3994,7 @@
       <c r="AA80" s="6"/>
       <c r="AB80" s="6"/>
     </row>
-    <row r="81" spans="17:28" x14ac:dyDescent="1.05">
+    <row r="81" spans="17:28" x14ac:dyDescent="0.3">
       <c r="Q81" s="6"/>
       <c r="R81" s="6"/>
       <c r="S81" s="6"/>
@@ -3994,7 +4008,7 @@
       <c r="AA81" s="6"/>
       <c r="AB81" s="6"/>
     </row>
-    <row r="82" spans="17:28" x14ac:dyDescent="1.05">
+    <row r="82" spans="17:28" x14ac:dyDescent="0.3">
       <c r="V82" s="6"/>
       <c r="W82" s="6"/>
       <c r="X82" s="6"/>
@@ -4003,7 +4017,7 @@
       <c r="AA82" s="6"/>
       <c r="AB82" s="6"/>
     </row>
-    <row r="83" spans="17:28" x14ac:dyDescent="1.05">
+    <row r="83" spans="17:28" x14ac:dyDescent="0.3">
       <c r="V83" s="6"/>
       <c r="W83" s="6"/>
       <c r="X83" s="6"/>
@@ -4012,7 +4026,7 @@
       <c r="AA83" s="6"/>
       <c r="AB83" s="6"/>
     </row>
-    <row r="84" spans="17:28" x14ac:dyDescent="1.05">
+    <row r="84" spans="17:28" x14ac:dyDescent="0.3">
       <c r="V84" s="6"/>
       <c r="W84" s="6"/>
       <c r="X84" s="6"/>
@@ -4023,11 +4037,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M40:N44"/>
-    <mergeCell ref="A13:A56"/>
-    <mergeCell ref="B45:B56"/>
-    <mergeCell ref="B13:B27"/>
-    <mergeCell ref="B28:B44"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="F11:P11"/>
     <mergeCell ref="A11:A12"/>
@@ -4036,6 +4045,11 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="D11:D12"/>
+    <mergeCell ref="M40:N44"/>
+    <mergeCell ref="A13:A56"/>
+    <mergeCell ref="B45:B56"/>
+    <mergeCell ref="B13:B27"/>
+    <mergeCell ref="B28:B44"/>
     <mergeCell ref="M51:N51"/>
     <mergeCell ref="M45:N50"/>
     <mergeCell ref="M28:N39"/>
@@ -4050,7 +4064,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA209645-067A-4672-8BAA-D8A1816FA075}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
